--- a/data/current_election_results.xlsx
+++ b/data/current_election_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,66 +456,6 @@
         <is>
           <t>Beteiligung %</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Zürich</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Adliswil</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>9758</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3800</v>
-      </c>
-      <c r="G2" t="n">
-        <v>54.2169</v>
-      </c>
-      <c r="H2" t="n">
-        <v>85.05840000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>230</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Zürich</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Winterthur</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>72221</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>46.1538</v>
-      </c>
-      <c r="H3" t="n">
-        <v>90.00149999999999</v>
       </c>
     </row>
   </sheetData>
